--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_005/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_005/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -449,11 +454,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G4" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -489,11 +489,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H5" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -540,6 +535,41 @@
       </text>
     </comment>
     <comment ref="I6" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="H7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="I7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1291,17 +1321,17 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Artemis-CLPS Rover Battery Enclosure Frame Structural Assessment</t>
+          <t>Artemis-CLPS Rover Battery Enclosure Frame Structural Modeling</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Finite element model of rover battery enclosure frame for quasi-static launch load and modal frequency evaluation</t>
+          <t>Quasi-static launch load structural assessment and modal frequency clearance for rover battery enclosure frame</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>The FEA model (FEA-RBP-023) is used to make go/no-go decisions on the battery enclosure frame design under combined 12g vertical and 8g lateral quasi-static launch accelerations, and to verify that the first flexible mode exceeds 160 Hz to avoid coupling with avionics stack modes. The model drives bolt-size selection, fillet radii, and local stiffener placements.</t>
+          <t>The finite element model of the rover battery enclosure frame (Model ID: FEA-RBP-023) is used to make go/no-go decisions on the current frame design under combined 12g vertical and 8g lateral quasi-static launch accelerations, and to verify that the first flexible mode frequency exceeds 160 Hz to avoid coupling with avionics shelf modes. The model drives bolt-size selection, lug fillet radii, and stiffener placement decisions.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1339,9 +1369,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md (Rover Battery Enclosure Frame — Structural Modeling Credibility Report, Project Artemis-CLPS Rover Power Subsystem, Model ID FEA-RBP-023, Date 2026-07-22, prepared by Structures Simulation Group, JSC)</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1460,7 +1490,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Static Margin and Modal Frequency Acceptance Requirements</t>
+          <t>Structural Acceptance Requirements for Battery Enclosure Frame</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1470,7 +1500,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Von Mises stress must remain below allowable with minimum static margin of 0.05 under 12g vertical and 8g lateral combined; first flexible mode must exceed 160 Hz to avoid avionics coupling.</t>
+          <t>Von Mises stress must remain below the material allowable (355 MPa) with a minimum static margin of 0.05 at room temperature under combined 12g vertical and 8g lateral loads; first flexible mode must exceed 160 Hz to avoid avionics coupling.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1492,12 +1522,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>FEA-RBP-023 Ansys Mechanical Finite Element Model</t>
+          <t>FEA-RBP-023 Finite Element Model</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Ansys Mechanical 2024 R2 linear elastic FEA model of the 6061-T6 aluminum battery enclosure frame, including pretension bolt elements, modal extraction, and quasi-static load cases.</t>
+          <t>Ansys Mechanical 2024 R2 linear elastic FEA model of the 6061-T6 aluminum battery enclosure frame; tetrahedral and hexahedral second-order elements; pretension bolts; modal and quasi-static load cases.</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1539,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>DCR-STR-1109 Data Curation Record</t>
+          <t>Data Curation Record DCR-STR-1109</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Curated input dataset including launch environment accelerations (LE-2026-17), material properties (MMPDS-17), bolt preload (ME-PR-602 Rev C), and mass distribution, with traceability metadata.</t>
+          <t>Archive of all external input data including launch environment loads (LE-2026-17), material properties (MMPDS-17), bolt preload procedure (ME-PR-602 Rev C), and associated traceability metadata.</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1556,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Proto-1 Bench Test Dataset</t>
+          <t>Bench Correlation Test — Proto-1 Frame</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Static strain gauge measurements and impact hammer modal test results from the Proto-1 representative frame subassembly, including strain at lug fillet and midspan, and first two modal frequencies.</t>
+          <t>Static pull test and impact hammer modal test data from Proto-1 frame on steel plate fixture; strain gage measurements at two high-gradient locations and one global bending location; roving triax accelerometer modal identification.</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1573,12 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Latin Hypercube Uncertainty Study Run Log RL-023</t>
+          <t>Latin Hypercube Uncertainty Study Run Log</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>500-sample LHS uncertainty propagation results for hotspot stress and first eigenfrequency under parameter variations in E, yield strength, bolt preload, and electronics mass.</t>
+          <t>500-sample Latin Hypercube propagation over material stiffness, yield strength, bolt preload, and electronics mass variability; results including 95th percentile hotspot stress (324 MPa) and 5th percentile first mode frequency (171.1 Hz).</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1985,7 +2015,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Static Strain Gauge Correlation — Bench Pull Test</t>
+          <t>Mesh Convergence Study — Hotspot Stress</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2000,12 +2030,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Deadweight and hydraulic actuator applied equivalent 12g vertical and 8g lateral loads to the Proto-1 frame. Peak microstrain at lug fillet gage and midspan side rail gage were compared between model and test.</t>
+          <t>Three-level mesh refinement study on the lug fillet hotspot von Mises stress: coarse (185k elements, 308 MPa), medium (428k elements, 297 MPa), fine (1130k elements, 294 MPa). Richardson extrapolation performed to estimate residual discretization error.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Measured microstrain from EA-06-063QY-120 strain gauges on Proto-1 frame</t>
+          <t>Richardson extrapolation asymptotic limit; effective convergence order p ≈ 1.8</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2015,12 +2045,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Parameter variation via Latin Hypercube Sampling (500 samples); ±5% yield, ±3% E, ±10% bolt preload</t>
+          <t>Richardson extrapolation</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Lug fillet: measured 1600 με vs. predicted 1475 με (−7.8%); side rail: measured 642 με vs. predicted 606 με (−5.6%)</t>
+          <t>1.0% change from medium to fine mesh; estimated residual mesh error ~1.8% on medium mesh hotspot stress</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2032,7 +2062,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Modal Frequency and Mode Shape Correlation — Impact Hammer Test</t>
+          <t>Static Strain Correlation — Bench Pull Test</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2042,12 +2072,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Impact hammer test with roving triax accelerometers identified first two bending/torsion modes of the Proto-1 frame mounted on the steel fixture. Predicted frequencies and MAC values compared to test.</t>
+          <t>Comparison of FEA-predicted microstrain to strain gage measurements at the critical lug fillet and at the side rail midspan under equivalent 12g vertical and 8g lateral loading applied via deadweight frame and calibrated hydraulic actuator on Proto-1 frame.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>PCB 352C65 accelerometer measurements; identified modal frequencies and mode shapes from Proto-1 impact test</t>
+          <t>Measured strain gage data (EA-06-063QY-120) on Proto-1 bench article</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2055,14 +2085,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Sensitivity study shows first mode ranges 171–180 Hz across parameter distribution</t>
-        </is>
-      </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>Mode 1: test 182 Hz vs. predicted 175 Hz (−3.8%); Mode 2: test 233 Hz vs. predicted 229 Hz (−1.7%); MAC &gt; 0.95 for first two modes</t>
+          <t>Lug fillet: measured 1600 με, predicted 1475 με (−7.8%); side rail: measured 642 με, predicted 606 με (−5.6%)</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2074,7 +2099,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study — Hotspot Stress Richardson Extrapolation</t>
+          <t>Modal Frequency and Mode Shape Correlation — Impact Hammer Test</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2084,27 +2109,22 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Three-level mesh refinement (coarse 185k, medium 428k, fine 1130k elements) evaluated hotspot von Mises stress at lug fillet and global displacement marker. Richardson extrapolation used to estimate residual discretization error.</t>
+          <t>Comparison of FEA-predicted natural frequencies and mode shapes against impact hammer test results from Proto-1 frame with roving triax accelerometers. First two modes assessed; MAC values computed.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Asymptotic convergence; Richardson extrapolation with effective order p ≈ 1.8</t>
+          <t>Impact hammer modal test (PCB 352C65 accelerometers) on Proto-1 with steel plate fixture</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>Richardson extrapolation</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>Stress change medium-to-fine: 1.0%; displacement change medium-to-fine: 0.6%; estimated residual mesh error on hotspot stress ~1.8%</t>
+          <t>Mode 1: test 182 Hz vs. predicted 175 Hz (−3.8%); Mode 2: test 233 Hz vs. predicted 229 Hz (−1.7%); MAC &gt;0.95 for first two modes</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2116,7 +2136,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Uncertainty Propagation — Static Margin and Modal Frequency</t>
+          <t>Latin Hypercube Sensitivity and Uncertainty Propagation — Case 1</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2126,12 +2146,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>500-sample Latin Hypercube study propagating uncertainties in E, yield strength, bolt preload, and electronics mass through the medium mesh Case 1 model. 95th percentile stress and 5th percentile first frequency evaluated against design thresholds.</t>
+          <t>500-sample Latin Hypercube study propagating variability in Young's modulus, yield strength, bolt preload, and electronics mass through the medium-mesh FEA model for the critical combined load case. Results characterize spread in hotspot stress and first modal frequency.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Design requirements: static margin ≥ 0.05; first mode ≥ 160 Hz</t>
+          <t>Design allowable 355 MPa (static margin requirement ≥0.05); modal clearance requirement &gt;160 Hz</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2141,15 +2161,52 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Latin Hypercube Sampling (500 samples, SEED-STR-20260714)</t>
+          <t>Latin Hypercube Sampling (500 samples)</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>95th percentile stress 324 MPa → static margin 0.09 (vs. required 0.05); 5th percentile first mode 171 Hz (vs. required 160 Hz); P(stress &gt; yield) ≈ 1.7%</t>
+          <t>Hotspot stress 95th percentile 324 MPa → static margin 0.09; first mode 5th percentile 171.1 Hz (exceeds 160 Hz by 11.1 Hz)</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Solver Convergence and Numerical Checks</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>ValidationResult</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Assessment of iterative solver residuals, contact stability, energy balance, and independent rerun reproducibility for the static and modal analysis steps.</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Internal solver convergence targets; independent rerun on separate workstation (Ansys 2024 R1)</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>Force residual reduced 7 orders of magnitude; displacement residual 6 orders; energy ratio 0.999; independent rerun frequency difference &lt;0.6%, hotspot stress difference &lt;1.2%</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2296,16 +2353,16 @@
         <v>3</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver with documented version control and archive; model files stored with checksum traceability.</t>
+          <t>Simulation software is a verified commercial solver with traceable version control and archived model files.</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Ansys Mechanical 2024 R2 is a commercially certified solver with established quality processes. Model archive is stored in PLM Vault record PLM-STR-4473 with solver input checksum 8F1C-BC92. Post-processing scripts are tracked in Git repo STR-FEA-Tools at commit 3a4c2e7. A rerun on a separate workstation (Ansys 2024 R1) reproduced results within 0.6% for frequency and 1.2% for stress, confirming reproducibility. No explicit ISO certification documentation is cited, limiting the level to 3.</t>
+          <t>Ansys Mechanical 2024 R2 is a commercial FEA solver with established quality processes. Model archive is stored in PLM Vault record PLM-STR-4473 with solver input checksum 8F1C-BC92. Post-processing scripts are tracked in Git repo STR-FEA-Tools at commit 3a4c2e7. An independent rerun on a separate workstation (Ansys 2024 R1) confirmed results within 0.6% (frequency) and 1.2% (stress), demonstrating reproducibility. Version traceability is explicit; no regression test suite results are documented, but commercial certification and rerun verification provide substantial evidence.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2330,16 +2387,16 @@
         <v>2</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Solver behavior verified via internal consistency checks and cross-version rerun; no independent MMS or analytical benchmark documented.</t>
+          <t>Code correctly solves governing linear elasticity and eigenvalue equations, supported by benchmark or analytical solution comparison.</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>No formal Method of Manufactured Solutions or analytical benchmark comparison is reported. However, cross-version rerun (2024 R1 vs. 2024 R2) showing &lt;0.6% frequency and &lt;1.2% stress differences provides indirect confirmation of code correctness. Residual force balance and mass/stiffness orthogonality checks (within 0.3%) are noted, but these are solver convergence checks rather than code verification per se. Level 2 is appropriate given the absence of explicit benchmark problems.</t>
+          <t>No explicit comparison to analytical solutions or method of manufactured solutions is reported. However, standard Ansys Mechanical solvers (sparse direct, Lanczos eigensolver) are well-established commercial implementations with broad benchmark history. Mass and stiffness orthogonality checks passed within 0.3% tolerance for the modal step. The independent rerun on a different workstation and solver minor version (2024 R1 vs. 2024 R2) produced consistent results, providing indirect code verification evidence. Absence of project-specific analytical benchmarks limits the achieved level.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2368,12 +2425,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated with quantified residual error estimate at the quantity of interest.</t>
+          <t>Mesh convergence demonstrated at the critical quantity of interest (hotspot stress) with quantified residual error estimate.</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>A three-level mesh refinement study (185k, 428k, 1130k elements) was performed. Hotspot stress changed by 1.0% from medium to fine; global displacement changed by 0.6%. Richardson extrapolation with effective order p ≈ 1.8 yields an estimated residual mesh error of ~1.8% on the hotspot stress for the adopted medium mesh. Stress contours stabilized in shape between medium and fine. Element quality metrics reported (aspect ratio 1.8, minimum Jacobian 0.42). This constitutes thorough, quantified evidence of discretization adequacy.</t>
+          <t>A three-level mesh refinement study was performed (185k, 428k, 1130k elements). Hotspot stress changed from 308 to 297 to 294 MPa across levels. Change from medium to fine is 1.0%; displacement change from medium to fine is 0.6%. Richardson extrapolation with effective order p ≈ 1.8 yielded an estimated residual mesh error of ~1.8% on the medium mesh hotspot stress. Stress contours stabilized in shape between medium and fine. A mesh convergence graph (Figure A2) is referenced. The medium mesh was selected for production runs with the residual error explicitly quantified and documented.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2402,12 +2459,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Residual targets met; solver convergence monitored and documented for all load cases and modal steps.</t>
+          <t>Iterative solver residuals demonstrate adequate convergence; no solver instabilities observed.</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Static step: average force residual reduced by 7 orders of magnitude, displacement residual by 6 orders; no line search failures; maximum 8 equilibrium iterations per substep. Pretension step converged with residual forces &lt;0.5 N/node and contact penetration &lt;0.003 mm (&lt;0.3% of element size). Modal step: Lanczos eigensolver mass and stiffness orthogonality checks within 0.3%. Total reaction at supports matches applied loads within 0.2%. Strain energy to external work ratio converged to 0.999. No chattering in contact. All convergence criteria are explicitly documented.</t>
+          <t>Static step: average force residual reduced by 7 orders of magnitude; displacement residual by 6 orders of magnitude. No line search failures; maximum 8 equilibrium iterations per substep. Preload step converged with residual forces &lt;0.5 N per node and contact penetration &lt;0.003 mm (&lt;0.3% of local element size). Modal step: Lanczos eigensolver with mass and stiffness orthogonality checks within 0.3%. Energy balance ratio converged to 0.999. Contact pressure distributions stabilized without chattering. Reaction force balance within 0.2% of applied loads. All checks are explicitly documented in the report.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2436,12 +2493,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Boundary conditions and model setup verified through independent checks and physical consistency tests.</t>
+          <t>Model setup is independently reviewable and boundary conditions are verifiable against physical test configuration.</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Boundary conditions are documented and physically justified: fixed MPC supports replicate deck rigidity (deck stiffness estimated &gt;10× frame stiffness; test fixture confirmed ≥12× stiffer than frame). Load cases are clearly enumerated. Bolt pretension is explicitly represented. Residual force balance confirms load application correctness. CAD geometry simplifications (sub-0.8 mm fillets, cable bosses) are justified by sensitivity studies. No formal independent third-party review of the model setup is documented, which limits the level to 3 rather than 4.</t>
+          <t>Boundary conditions are described in detail: multi-point constraints at lug bore nodes replicating deck rigidity, pretension sections for six M6 bolts, frictionless footpad contact. Fixture stiffness was separately measured and confirmed to be ≥12× stiffer than the frame for the first two bending modes, validating the fixed-support idealization. The test fixture replicated the rover deck hole pattern. Suppressed geometry features (fillets &lt;0.8 mm, cable bosses) are justified by comparison runs showing &lt;1% influence on global stiffness. All files are archived in PLM Vault with hash checksum. No explicit independent third-party review or formal checklist is documented, limiting the level.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2470,12 +2527,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations and constitutive model appropriate for loading regime; idealizations justified with supporting evidence.</t>
+          <t>Mathematical model (linear elasticity, modal eigenvalue) is appropriate for the physics of quasi-static launch loading; assumptions are documented and justified.</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Linear elastic constitutive model is selected on the basis that peak stresses are required to remain below yield, and the bench test confirmed no plastic offset post-unload. The quasi-static acceleration approach is justified by the loading type. Bonded contact at lug bores and frictionless footpad contact are rationalized by the load case and pretension. Omission of thread detail and sub-mm fillets is justified by sensitivity studies and test correlation. Temperature-dependent modulus scaling is included within the 20–50°C operating range. Documented limitations (no random vibration fatigue, no thermal-mechanical coupling) are clearly stated. Evidence is adequate but not comprehensive (no turbulence or fluid models to assess; structural physics is relatively straightforward).</t>
+          <t>Linear elastic constitutive model is justified by the requirement that stresses remain below yield and by post-test observation of no plastic offset in strain readings. Pretension elements represent bolt preload explicitly. Temperature effects on modulus are represented by linear scaling of E. Omission of thread detail and gasket behavior is explicitly acknowledged as outside scope. The elastic assumption is further supported by the sensitivity study showing the 95th percentile stress (324 MPa) remains below the yield strength distribution mean (276 MPa yield; allowable 355 MPa). Frictionless contact at footpads and bonded contact at lug bores are physically justified. Limitations (random vibration, thermal extremes, fastener thread detail) are clearly documented in §14.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2504,12 +2561,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>All primary inputs traceable to authoritative sources with characterized uncertainties.</t>
+          <t>Material properties, loads, and boundary condition inputs are traceable to authoritative sources with quantified variability.</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Launch accelerations from LE-2026-17 Table 4-3 (3-sigma quasi-static). Material properties (E, yield, Poisson's ratio) from MMPDS-17 with stated variabilities (±3% E, ±5% yield). Bolt preload from torque procedure ME-PR-602 Rev C with ±10% range. Mass distribution allocated from CAD and vendor specs. Thermal modulus slope from NASA/TP-2010-216637. All inputs stored in DCR-STR-1109 with metadata linking to specific table/figure numbers. Uncertainties are characterized and propagated. This is thorough input documentation with quantified uncertainties.</t>
+          <t>Inertial loads from LE-2026-17 Table 4-3 (3-sigma quasi-static). Material properties (E = 69.0 GPa, yield = 276 MPa, ν = 0.33) from MMPDS-17 Sheet 2-1. Thermal modulus slope from NASA/TP-2010-216637. Bolt preload from ME-PR-602 Rev C torque procedure. Mass distribution allocated from CAD (frame) and vendor spec (battery). All data stored in Data Curation Record DCR-STR-1109 with metadata linking to specific table/figure numbers. Variability explicitly characterized: E ±3% (normal), yield ±5% COV (lognormal), bolt preload ±10% (uniform), electronics mass ±5% (uniform). Comprehensive traceability and quantified uncertainty on all major inputs achieved.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2538,12 +2595,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test articles are representative of the production configuration; sample size is characterized.</t>
+          <t>Test article is representative of the production design; sample size is adequate for the validation purpose.</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>A single Proto-1 frame was tested (one specimen). The report describes it as a representative article with a steel plate fixture replicating the rover deck hole pattern. Mass dummies were used. No statistical characterization of multiple specimens, no sample size justification, and no statement of production-representativeness beyond the geometry and hole pattern. A single test article limits confidence in test-to-population representativeness, giving level 2.</t>
+          <t>A single Proto-1 frame article was tested. The report does not document production-representativeness qualification, statistical characterization of article dimensions, or sample size justification beyond the single specimen. The fixture was verified as suitably rigid. The use of a single prototype limits statistical confidence in the test-based reference values. No mention of multiple test repeats or specimen-to-specimen variability assessment is made.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2572,12 +2629,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions are well-controlled and measured with calibrated instrumentation.</t>
+          <t>Test conditions are controlled and instrumented with calibrated equipment; measurement uncertainty is documented.</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Static pull test used deadweight frame and calibrated hydraulic actuator. Strain gauges (EA-06-063QY-120) were bonded at predicted high-gradient regions. Modal test used PCB 352C65 triax accelerometers with roving impact hammer. First mode damping ratio identified at 1.1%. Fixture stiffness independently characterized and confirmed to be ≥12× frame stiffness. Test standard or instrument calibration certificates are not explicitly cited, which prevents assignment of level 4, but instrumentation types are identified and the test setup is well described.</t>
+          <t>Static loads applied via deadweight frame and calibrated hydraulic actuator. Strain gages (EA-06-063QY-120) bonded at high-gradient locations predicted by analysis. Modal test used calibrated PCB 352C65 roving triax accelerometers; 1.1% damping ratio identified. Fixture stiffness independently characterized. Test identified first two modes with MAC &gt;0.95. However, explicit measurement uncertainty values for strain gages and accelerometers (calibration certificates, uncertainty budgets) are not reported in the document, limiting the achieved level.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2606,12 +2663,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model inputs used in validation match measured test conditions; boundary condition matching documented.</t>
+          <t>Model inputs for the correlation runs match the test conditions; boundary conditions replicate the test fixture setup.</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>The correlation model applied boundary conditions consistent with the bench test setup: fixed MPC at fixture bolt patterns, mass dummies at their as-tested locations, identical pretension values. Fixture flexibility was measured and confirmed negligible. Damping of 1% modal was assigned based on test-identified 1.1% damping ratio. The model predictions for the test configuration were explicitly separated from the flight predictions. Parameter spreads from the sensitivity study are stated to cover the observed test-to-model discrepancies, providing a closing argument. Some uncertainty propagation from test measurement uncertainty to the equivalency check is implicit rather than fully formalized.</t>
+          <t>The correlation analysis used identical boundary conditions to the test: steel plate fixture geometry replicated in the model, fixed-support MPC at bolt hole patterns, same mass dummy configuration. Fixture rigidity was confirmed at ≥12× frame stiffness for first two modes. Bolt pretension from ME-PR-602 Rev C is included in the correlation model. The load magnitudes (12g vertical, 8g lateral) are matched between test and analysis. No explicit uncertainty propagation from test measurement uncertainties into model input bounds is documented, but the sensitivity study bounds on E, preload, and mass capture the primary sources of discrepancy, and the report notes that parameter spreads are consistent with observed differences.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2640,12 +2697,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of model predictions to test measurements at multiple output locations; error metrics documented.</t>
+          <t>Quantitative comparison between model predictions and test measurements at multiple locations; discrepancies are within established bounds.</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Static case: lug fillet microstrain −7.8%, side rail microstrain −5.6% (two spatial locations). Modal: first mode frequency −3.8%, second mode −1.7%, MAC &gt; 0.95 for first two modes (four comparison quantities). Frequency response overlay shown in Figure A3. 95th percentile stress and 5th percentile frequency compared against design thresholds with explicit margin calculations. Histogram of 500-sample LHS shown in Figure A4. Comparisons are quantitative and multi-point. Uncertainty bands are present from the sensitivity study but formal statistical validation metrics (e.g., hypothesis tests, validation intervals) are not computed, limiting the level to 3.</t>
+          <t>Static strain comparison at two locations: lug fillet (−7.8%) and side rail (−5.6%). Modal frequency comparison for two modes: Mode 1 −3.8%, Mode 2 −1.7%. MAC values &gt;0.95 for first two mode shapes. Frequency response overlay (Figure A3) and histogram of LHS stress spread (Figure A4) are referenced. The sensitivity study demonstrates that the observed static strain differences (up to 7.8%) are consistent with plausible parameter variability. No formal statistical validation metric (e.g., u-pooled, MSWD) is applied; the comparison is quantitative but judgment-based rather than formal-statistical. Multiple comparison points and two QoI types (strain and frequency) strengthen the evidence.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2674,12 +2731,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs directly address the acceptance criteria and are measurable both computationally and experimentally.</t>
+          <t>Model QoIs (hotspot von Mises stress, first modal frequency) directly address the design acceptance criteria and are measurable in both analysis and test.</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>The two primary QoIs — hotspot von Mises stress (driving static margin) and first flexible mode frequency (driving avionics separation) — directly map to the two stated design acceptance requirements. Both are computed by the FEA model and were measured in the bench test (stress via strain gauge conversion, frequency via accelerometer/impact hammer). The sensitivity study and 95th percentile stress are used directly in the margin calculation. Secondary QoIs (displacements, contact pressures) are also tracked. The QoIs are tightly coupled to the decision criteria.</t>
+          <t>The two primary QoIs — hotspot von Mises stress (compared to the 355 MPa allowable) and first flexible mode frequency (compared to the 160 Hz threshold) — directly map to the stated design acceptance requirements. Both are computed in the FEA and measured in the bench test (stress via microstrain and modal frequency via impact hammer). The sensitivity study produces distributions for both QoIs from which margins are computed against requirements. The QoIs are unambiguous, directly decision-relevant, and measurable both computationally and experimentally.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2708,12 +2765,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation test conditions cover the intended use loading regime, geometry, and assembly configuration.</t>
+          <t>Validation test conditions (geometry, loads, boundary conditions, material) are representative of the intended COU (quasi-static launch loads, on-rover mounted configuration).</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>The bench test used the same frame geometry (Proto-1), the same bolt pattern, the same fastener pretension procedure, and loads intended to replicate the quasi-static 12g vertical and 8g lateral case. The fixture was confirmed to be representative of the deck boundary condition. Modal test covered the first two modes relevant to the 160 Hz requirement. Gaps relative to the full COU: only one temperature condition (room temperature, not the full 20–50°C envelope); only quasi-static loading (no broadband random vibration or shock validation); single prototype article. These gaps are documented in the limitations section, and the report explicitly excludes thermal extremes and random vibration from the COU, bounding the applicability to conditions covered by the validation.</t>
+          <t>The bench test used the Proto-1 frame with a steel plate fixture replicating the rover deck hole pattern, the same M6 bolt pattern, and equivalent load magnitudes. The load application method (deadweight plus calibrated hydraulic actuator) replicates the combined vertical and lateral acceleration environment. The same temperature range (room temperature, 20–50°C) applies to both the COU and the test. Gaps exist: the on-rover mounted configuration differs from the steel plate fixture (deck flexibility not identical), random vibration and shock are not tested, and thermal extremes of the lunar environment are explicitly excluded. The validation is well-matched to the quasi-static COU but does not cover all aspects of the full operational envelope; limitations are clearly documented.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2898,7 +2955,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The FEA model FEA-RBP-023 meets the stated acceptance criteria for its context of use. The 95th-percentile hotspot stress under the combined 12g/8g load case yields a static margin of 0.09, exceeding the required 0.05 minimum. The 5th-percentile first flexible mode at 171 Hz exceeds the 160 Hz separation requirement by 11 Hz. Bench test correlation shows discrepancies of −7.8% and −5.6% in strain and −3.8% and −1.7% in frequency, consistent with characterized parameter uncertainties. Mesh discretization error is quantified at ~1.8% via Richardson extrapolation. Inputs are traceable to authoritative sources with documented uncertainties propagated through a 500-sample LHS. Known limitations (thread detail, thermal extremes, random vibration fatigue) are explicitly scoped out of the COU and flagged for future work. The model is accepted for use in go/no-go decisions on the current design configuration, contingent on maintaining the specified M6 fastener torque range and no changes to bolt pattern, fillet radii above 1 mm, or mass placement.</t>
+          <t>The FEA model of the rover battery enclosure frame (FEA-RBP-023) is accepted for its stated context of use: quasi-static launch load structural assessment and first modal frequency clearance. All acceptance criteria are met: the 95th percentile hotspot stress yields a static margin of 0.09 (requirement ≥0.05), and the 5th percentile first mode frequency is 171.1 Hz (requirement &gt;160 Hz). Model predictions correlate with bench test measurements within 7.8% for static strain and 3.8% for modal frequency, with MAC &gt;0.95. Mesh convergence is demonstrated with a quantified residual error of ~1.8%. Solver convergence, energy balance, and independent reproducibility checks all pass. Input data are fully traceable to authoritative sources with quantified variability. Acceptance is contingent on maintaining the specified M6 fastener torque range (ME-PR-602 Rev C), no changes to fillet radii, bolt pattern, or mass distribution beyond documented bounds, and restriction of use to the quasi-static and modal COU only — broadband random vibration, shock, thermal extremes, and fastener thread-level assessments remain out of scope and require separate dedicated analyses.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
